--- a/config/pokedex_advance.xlsx
+++ b/config/pokedex_advance.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="pokedex_advance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pokedex_advance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1194,15 +1194,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>&lt;cn;tw;en;vn;th;kr&gt;</t>
@@ -1304,7 +1300,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>仲間5体を集める</t>
+          <t>收集5名伙伴</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1324,7 +1320,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員のHP+#C0xFF60C456#350</t>
+          <t>#C0xFF5B545B#所有伙伴的HP+#C0xFF60C456#350</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1357,7 +1353,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1373,7 +1368,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1383,7 +1377,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>仲間10体を集める</t>
+          <t>收集10名伙伴</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1403,7 +1397,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の物防+#C0xFF60C456#120</t>
+          <t>#C0xFF5B545B#全体伙伴的物防+#C0xFF60C456#120</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1436,7 +1430,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1452,7 +1445,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1462,7 +1454,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1482,7 +1474,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の特防+#C0xFF60C456#150</t>
+          <t>#C0xFF5B545B#全体伙伴的特防+#C0xFF60C456#150</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1515,7 +1507,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1531,7 +1522,6 @@
           <t>150</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1541,7 +1531,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1561,7 +1551,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の会心耐性+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#全体伙伴的暴击抵抗+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1594,7 +1584,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1610,7 +1599,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1620,7 +1608,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>仲間50体を集める</t>
+          <t>收集50名伙伴</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1640,7 +1628,7 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の物防+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体的物防+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1673,7 +1661,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>0</t>
@@ -1689,7 +1676,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1699,7 +1685,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>仲間70体を集める</t>
+          <t>收集70名伙伴</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1719,7 +1705,7 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の特防+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体的特防+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1752,7 +1738,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1768,7 +1753,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>仲間100体を集める</t>
+          <t>收集100名伙伴</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1798,7 +1782,7 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の会心耐性+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#全体伙伴的暴击抵抗+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1831,7 +1815,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>0</t>
@@ -1847,7 +1830,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1857,7 +1839,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>仲間150体を集める</t>
+          <t>收集150名伙伴</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1877,7 +1859,7 @@
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の物理ダメージ軽減+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体物理伤害减轻+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1890,7 +1872,6 @@
           <t>#C0xFF5B545B#All Allies' Phys DMG Reduction +#C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 피해감소 증가: #C0xFF60C456#3%</t>
@@ -1906,7 +1887,6 @@
           <t>150</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>0</t>
@@ -1922,7 +1902,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1932,7 +1911,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>仲間200体を集める</t>
+          <t>收集200名伙伴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1952,7 +1931,7 @@
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の特殊ダメージ軽減+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#全体伙伴特殊伤害减轻+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1965,7 +1944,6 @@
           <t>#C0xFF5B545B#All Allies' Sp. DMG Reduction +#C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 특수피해감소 증가: #C0xFF60C456#3%</t>
@@ -1981,7 +1959,6 @@
           <t>200</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>0</t>
@@ -1997,7 +1974,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2007,7 +1983,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2027,7 +2003,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2080,7 +2056,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2090,7 +2065,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2110,7 +2085,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2163,7 +2138,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2173,7 +2147,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2193,7 +2167,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2246,7 +2220,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2256,7 +2229,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2276,7 +2249,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2329,7 +2302,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2339,7 +2311,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2359,7 +2331,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2412,7 +2384,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2422,7 +2393,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2442,7 +2413,7 @@
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2495,7 +2466,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2505,7 +2475,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2525,7 +2495,7 @@
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2578,7 +2548,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2588,7 +2557,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2608,7 +2577,7 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2661,7 +2630,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2671,7 +2639,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>仲間5体を集める</t>
+          <t>收集5名伙伴</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2691,7 +2659,7 @@
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2744,7 +2712,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2754,7 +2721,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>仲間10体を集める</t>
+          <t>收集10名伙伴</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2774,7 +2741,7 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2827,7 +2794,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2837,7 +2803,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2857,7 +2823,7 @@
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2910,7 +2876,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2920,7 +2885,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2940,7 +2905,7 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2993,7 +2958,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3003,7 +2967,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>仲間33体を集める</t>
+          <t>收集33名伙伴</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3023,7 +2987,7 @@
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3076,7 +3040,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3086,7 +3049,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>仲間36体を集める</t>
+          <t>收集36名伙伴</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3106,7 +3069,7 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3159,7 +3122,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3169,7 +3131,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>仲間5体を集める</t>
+          <t>收集5名伙伴</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3189,7 +3151,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的树属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3242,7 +3204,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3252,7 +3213,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>仲間10体を集める</t>
+          <t>收集10名伙伴</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3272,7 +3233,7 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的树属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3325,7 +3286,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3335,7 +3295,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3355,7 +3315,7 @@
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的树属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3408,7 +3368,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3418,7 +3377,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3438,7 +3397,7 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3491,7 +3450,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3501,7 +3459,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3521,7 +3479,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3574,7 +3532,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3584,7 +3541,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3604,7 +3561,7 @@
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3657,7 +3614,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3667,7 +3623,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3687,7 +3643,7 @@
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3740,7 +3696,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3750,7 +3705,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3770,7 +3725,7 @@
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3823,7 +3778,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3833,7 +3787,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3853,7 +3807,7 @@
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3906,7 +3860,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3916,7 +3869,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3936,7 +3889,7 @@
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3989,7 +3942,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3999,7 +3951,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4019,7 +3971,7 @@
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4072,7 +4024,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4082,7 +4033,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4102,7 +4053,7 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4155,7 +4106,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4165,7 +4115,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4185,7 +4135,7 @@
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4238,7 +4188,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4248,7 +4197,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>仲間5体を集める</t>
+          <t>收集5名伙伴</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4268,7 +4217,7 @@
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4321,7 +4270,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4331,7 +4279,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>仲間10体を集める</t>
+          <t>收集10名伙伴</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4351,7 +4299,7 @@
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4404,7 +4352,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4414,7 +4361,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>仲間15体を集める</t>
+          <t>收集15名伙伴</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4434,7 +4381,7 @@
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4487,7 +4434,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4497,7 +4443,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4517,7 +4463,7 @@
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4570,7 +4516,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4580,7 +4525,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>仲間5体を集める</t>
+          <t>收集5名伙伴</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4600,7 +4545,7 @@
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4653,7 +4598,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4663,7 +4607,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>仲間10体を集める</t>
+          <t>收集10名伙伴</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4683,7 +4627,7 @@
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4736,7 +4680,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4746,7 +4689,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>仲間15体を集める</t>
+          <t>收集15名伙伴</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4766,7 +4709,7 @@
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4819,7 +4762,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4829,7 +4771,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4849,7 +4791,7 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4902,7 +4844,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4912,7 +4853,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4932,7 +4873,7 @@
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4985,7 +4926,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4995,7 +4935,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5015,7 +4955,7 @@
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5068,7 +5008,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5078,7 +5017,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5098,7 +5037,7 @@
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5151,7 +5090,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5161,7 +5099,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5181,7 +5119,7 @@
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5234,7 +5172,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5244,7 +5181,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5264,7 +5201,7 @@
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的法属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5317,7 +5254,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5327,7 +5263,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5347,7 +5283,7 @@
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的法属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5400,7 +5336,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5410,7 +5345,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5430,7 +5365,7 @@
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的法属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5483,7 +5418,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5493,7 +5427,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5513,7 +5447,7 @@
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5566,7 +5500,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5576,7 +5509,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5596,7 +5529,7 @@
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5649,7 +5582,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5659,7 +5591,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5679,7 +5611,7 @@
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5732,7 +5664,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5742,7 +5673,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5762,7 +5693,7 @@
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5815,7 +5746,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5825,7 +5755,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5845,7 +5775,7 @@
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5898,7 +5828,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5908,7 +5837,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5928,7 +5857,7 @@
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5981,7 +5910,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5991,7 +5919,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6011,7 +5939,7 @@
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6064,7 +5992,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6074,7 +6001,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6094,7 +6021,7 @@
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6147,7 +6074,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6157,7 +6083,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6177,7 +6103,7 @@
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6230,7 +6156,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6240,7 +6165,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>仲間9体を集める</t>
+          <t>收集9名伙伴</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6260,7 +6185,7 @@
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6313,7 +6238,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6323,7 +6247,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6343,7 +6267,7 @@
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6396,7 +6320,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6406,7 +6329,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>仲間15体を集める</t>
+          <t>收集15名伙伴</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6426,7 +6349,7 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6479,7 +6402,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6489,7 +6411,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6509,7 +6431,7 @@
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6562,7 +6484,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6572,7 +6493,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6592,7 +6513,7 @@
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6645,7 +6566,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6655,7 +6575,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6675,7 +6595,7 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6728,7 +6648,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6738,7 +6657,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6758,7 +6677,7 @@
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6811,7 +6730,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6821,7 +6739,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6841,7 +6759,7 @@
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6894,7 +6812,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6904,7 +6821,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6924,7 +6841,7 @@
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6977,7 +6894,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6987,7 +6903,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>仲間9体を集める</t>
+          <t>收集9名伙伴</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7007,7 +6923,7 @@
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7060,7 +6976,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7070,7 +6985,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>仲間15体を集める</t>
+          <t>收集15名伙伴</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7090,7 +7005,7 @@
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7143,7 +7058,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7153,7 +7067,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7173,7 +7087,7 @@
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7226,7 +7140,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7236,7 +7149,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7256,7 +7169,7 @@
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7309,7 +7222,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7319,7 +7231,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7339,7 +7251,7 @@
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7392,7 +7304,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7402,7 +7313,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7422,7 +7333,7 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7475,7 +7386,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7485,7 +7395,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>仲間3体を集める</t>
+          <t>收集三个伙伴</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7505,7 +7415,7 @@
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7558,7 +7468,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7568,7 +7477,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>仲間6体を集める</t>
+          <t>收集6名伙伴</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7588,7 +7497,7 @@
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7641,7 +7550,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7651,7 +7559,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>仲間9体を集める</t>
+          <t>收集9名伙伴</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7671,7 +7579,7 @@
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7724,7 +7632,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7734,7 +7641,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>仲間12体を集める</t>
+          <t>收集12名伙伴</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7754,7 +7661,7 @@
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7807,25 +7714,8 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
@@ -7834,7 +7724,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>仲間250体を集める</t>
+          <t>收集250名伙伴</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7854,7 +7744,7 @@
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の物防+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体的物防+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7867,7 +7757,6 @@
           <t>#C0xFF5B545B#All Allies' Phys DEF +#C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 방어 증가: #C0xFF60C456#3%</t>
@@ -7883,7 +7772,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>0</t>
@@ -7899,7 +7787,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7909,7 +7796,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>仲間300体を集める</t>
+          <t>收集300名伙伴</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7929,7 +7816,7 @@
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の特防+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体的特防+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7942,7 +7829,6 @@
           <t>#C0xFF5B545B#All Allies' Sp. DEF +#C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 특수방어 증가: #C0xFF60C456#3%</t>
@@ -7958,7 +7844,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>0</t>
@@ -7974,7 +7859,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7984,7 +7868,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>仲間350体を集める</t>
+          <t>收集350名伙伴</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8004,7 +7888,7 @@
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の会心耐性+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#全体伙伴的暴击抵抗+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8037,7 +7921,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>0</t>
@@ -8053,7 +7936,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8063,7 +7945,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>仲間400体を集める</t>
+          <t>收集400名伙伴</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8083,7 +7965,7 @@
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の物防+#C0xFF60C456#3%</t>
+          <t>#C0xFF5B545B#伙伴全体的物防+#C0xFF60C456#3%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8116,7 +7998,6 @@
           <t>400</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>0</t>
@@ -8132,10 +8013,8 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
       <c r="B88" s="1" t="inlineStr">
         <is>
           <t>仲間450体を集める</t>
@@ -8191,7 +8070,6 @@
           <t>450</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>0</t>
@@ -8207,10 +8085,8 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
       <c r="B89" s="1" t="inlineStr">
         <is>
           <t>仲間500体を集める</t>
@@ -8266,7 +8142,6 @@
           <t>500</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>0</t>
@@ -8282,10 +8157,8 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
       <c r="B90" s="1" t="inlineStr">
         <is>
           <t>仲間550体を集める</t>
@@ -8321,7 +8194,6 @@
           <t>#C0xFF5B545B#P.ATK of all Pokémons increases by #C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 피해감소 증가: #C0xFF60C456#3%</t>
@@ -8337,7 +8209,6 @@
           <t>550</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>0</t>
@@ -8353,10 +8224,8 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
       <c r="B91" s="1" t="inlineStr">
         <is>
           <t>仲間600体を集める</t>
@@ -8392,7 +8261,6 @@
           <t>#C0xFF5B545B#SP.ATK of all Pokémons increases by #C0xFF60C456#3%</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 특수피해감소 증가: #C0xFF60C456#3%</t>
@@ -8408,7 +8276,6 @@
           <t>600</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>0</t>
@@ -8424,25 +8291,8 @@
           <t>300</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -8451,7 +8301,7 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8471,7 +8321,7 @@
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8524,7 +8374,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8534,7 +8383,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8554,218 +8403,213 @@
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的无属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈一般系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Null DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thường tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 노말 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>仲間60体を集める</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>收集60全體精靈</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Collect 60 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 60마리 수집</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈一般系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Null DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Normal-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thường tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 노말 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>仲間60体を集める</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>收集60全體精靈</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Collect 60 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 60마리 수집</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>仲間80体を集める</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>收集80全體精靈</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Collect 80 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 80마리 수집</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈一般系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Normal-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thường tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 노말 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>仲間80体を集める</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>收集80全體精靈</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Collect 80 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 80마리 수집</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の無属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈一般系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Normal-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thường tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 노말 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8775,7 +8619,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8795,7 +8639,7 @@
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8848,7 +8692,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8858,7 +8701,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8878,7 +8721,7 @@
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8931,7 +8774,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8941,7 +8783,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>仲間60体を集める</t>
+          <t>收集60名伙伴</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8961,139 +8803,136 @@
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的火焰属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈火系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Flame DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Lửa tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 불꽃 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>仲間80体を集める</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>收集80全體精靈</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Collect 80 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 80마리 수집</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈火系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Flame DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Fire-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Lửa tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 불꽃 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>仲間80体を集める</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>收集80全體精靈</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Collect 80 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 80마리 수집</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の炎属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈火系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Fire-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Lửa tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 불꽃 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9103,7 +8942,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9123,7 +8962,7 @@
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -9176,7 +9015,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9186,7 +9024,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>仲間60体を集める</t>
+          <t>收集60名伙伴</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9206,7 +9044,7 @@
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の水属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的水属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9259,7 +9097,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9269,7 +9106,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9289,7 +9126,7 @@
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的树属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9342,7 +9179,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9352,7 +9188,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9372,297 +9208,290 @@
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的树属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈草系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Nature DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Cỏ tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 풀 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>仲間50体を集める</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>收集50全體精靈</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Collect 50 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 50마리 수집</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈草系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Nature DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Grass-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Cỏ tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 풀 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>仲間50体を集める</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>收集50全體精靈</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Collect 50 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 50마리 수집</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>仲間60体を集める</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>收集60全體精靈</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Collect 60 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 60마리 수집</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈草系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Grass-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Cỏ tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 풀 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>仲間60体を集める</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>收集60全體精靈</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Collect 60 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 60마리 수집</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>仲間70体を集める</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>收集70全體精靈</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Collect 70 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 70마리 수집</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈草系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Grass-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Cỏ tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 풀 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>仲間70体を集める</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>收集70全體精靈</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Collect 70 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 70마리 수집</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の木属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈草系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Grass-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Cỏ tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 풀 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9672,7 +9501,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9692,7 +9521,7 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9745,7 +9574,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9755,7 +9583,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9775,7 +9603,7 @@
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9828,7 +9656,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9838,7 +9665,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>仲間35体を集める</t>
+          <t>收集35名伙伴</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9858,218 +9685,213 @@
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的雷属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈電系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Bolt DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Điện tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 전기 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>仲間45体を集める</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>收集45全體精靈</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Collect 45 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 45마리 수집</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈電系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Bolt DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Electric-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Điện tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 전기 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr"/>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>仲間45体を集める</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>收集45全體精靈</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Collect 45 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 45마리 수집</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>仲間50体を集める</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>收集50全體精靈</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Collect 50 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 50마리 수집</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈電系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Electric-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Điện tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 전기 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>仲間50体を集める</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>收集50全體精靈</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Collect 50 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 50마리 수집</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の雷属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈電系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Electric-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Điện tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 전기 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10079,7 +9901,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10099,7 +9921,7 @@
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -10152,7 +9974,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10162,7 +9983,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10182,7 +10003,7 @@
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -10235,7 +10056,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10245,7 +10065,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -10265,7 +10085,7 @@
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -10318,7 +10138,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10328,7 +10147,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>仲間35体を集める</t>
+          <t>收集35名伙伴</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10348,139 +10167,136 @@
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的寒属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈冰系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Frost DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Băng tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 얼음 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>仲間40体を集める</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>收集40全體精靈</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Collect 40 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 40마리 수집</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈冰系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Frost DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Ice-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Băng tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 얼음 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>仲間40体を集める</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>收集40全體精靈</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Collect 40 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 40마리 수집</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の寒属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈冰系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Ice-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Băng tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 얼음 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10490,7 +10306,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10510,7 +10326,7 @@
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -10563,7 +10379,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10573,7 +10388,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10593,7 +10408,7 @@
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -10646,7 +10461,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10656,7 +10470,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>仲間35体を集める</t>
+          <t>收集35名伙伴</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10676,139 +10490,136 @@
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的战属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈格鬥系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Combat DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đấu tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 격투 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>仲間40体を集める</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>收集40全體精靈</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Collect 40 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 40마리 수집</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈格鬥系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Combat DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Fighting-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đấu tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 격투 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>仲間40体を集める</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>收集40全體精靈</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Collect 40 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 40마리 수집</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の戦属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈格鬥系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Fighting-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đấu tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 격투 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10818,7 +10629,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10838,7 +10649,7 @@
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10891,7 +10702,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10901,7 +10711,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10921,7 +10731,7 @@
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -10974,7 +10784,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10984,7 +10793,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>仲間50体を集める</t>
+          <t>收集50名伙伴</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -11004,139 +10813,136 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的毒属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈毒系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Toxin DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Độc tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 독 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>仲間60体を集める</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>收集60全體精靈</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Collect 60 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 60마리 수집</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈毒系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Toxin DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Poison-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Độc tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 독 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>仲間60体を集める</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>收集60全體精靈</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Collect 60 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 60마리 수집</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の毒属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈毒系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Poison-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Độc tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 독 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11146,7 +10952,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -11166,7 +10972,7 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -11219,7 +11025,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -11229,7 +11034,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -11249,218 +11054,213 @@
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的地属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈地面系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Earth DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đất tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 땅 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>仲間50体を集める</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>收集50全體精靈</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Collect 50 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 50마리 수집</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈地面系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Earth DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Ground-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đất tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 땅 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>仲間50体を集める</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>收集50全體精靈</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Collect 50 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 50마리 수집</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>仲間60体を集める</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>收集60全體精靈</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Collect 60 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 60마리 수집</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈地面系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Ground-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đất tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 땅 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>仲間60体を集める</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>收集60全體精靈</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Collect 60 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 60마리 수집</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の地属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈地面系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Ground-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đất tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 땅 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11470,7 +11270,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -11490,7 +11290,7 @@
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -11543,7 +11343,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11553,7 +11352,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -11573,218 +11372,213 @@
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的空属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈飛行系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Sky DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bay tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 비행 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>仲間55体を集める</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>收集55全體精靈</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Collect 55 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 55마리 수집</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈飛行系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Sky DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Flying-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bay tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 비행 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O131" t="inlineStr">
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr"/>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>仲間55体を集める</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>收集55全體精靈</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Collect 55 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 55마리 수집</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>仲間65体を集める</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>收集65全體精靈</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Collect 65 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 65마리 수집</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈飛行系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Flying-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bay tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 비행 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>仲間65体を集める</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>收集65全體精靈</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Collect 65 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 65마리 수집</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の空属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈飛行系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Flying-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bay tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 비행 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11794,7 +11588,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>仲間27体を集める</t>
+          <t>收集27名伙伴</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -11814,7 +11608,7 @@
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的法属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11867,7 +11661,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11877,7 +11670,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>仲間40体を集める</t>
+          <t>收集40名伙伴</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -11897,297 +11690,290 @@
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的法属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈超能系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Arcane DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Siêu tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 에스퍼 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>仲間50体を集める</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>收集50全體精靈</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Collect 50 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 50마리 수집</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈超能系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Arcane DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Psychic-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Siêu tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 에스퍼 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr"/>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>仲間50体を集める</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>收集50全體精靈</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Collect 50 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 50마리 수집</t>
-        </is>
-      </c>
-      <c r="F136" s="1" t="inlineStr">
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>仲間60体を集める</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>收集60全體精靈</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Collect 60 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 60마리 수집</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈超能系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Psychic-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Siêu tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 에스퍼 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr"/>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t>仲間60体を集める</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>收集60全體精靈</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Collect 60 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 60마리 수집</t>
-        </is>
-      </c>
-      <c r="F137" s="1" t="inlineStr">
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>仲間70体を集める</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>收集70全體精靈</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Collect 70 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 70마리 수집</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈超能系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Psychic-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I138" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Siêu tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 에스퍼 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>仲間70体を集める</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>收集70全體精靈</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Collect 70 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 70마리 수집</t>
-        </is>
-      </c>
-      <c r="F138" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の法属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈超能系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Psychic-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Siêu tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 에스퍼 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12197,7 +11983,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>仲間16体を集める</t>
+          <t>收集16名伙伴</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12217,7 +12003,7 @@
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -12270,7 +12056,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12280,7 +12065,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -12300,7 +12085,7 @@
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -12353,7 +12138,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -12363,7 +12147,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12383,218 +12167,213 @@
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的魅属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈蟲系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Allure DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bọ tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 벌레 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>仲間28体を集める</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>收集28全體精靈</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Collect 28 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 28마리 수집</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈蟲系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Allure DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Bug-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bọ tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 벌레 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>仲間28体を集める</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>收集28全體精靈</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Collect 28 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 28마리 수집</t>
-        </is>
-      </c>
-      <c r="F142" s="1" t="inlineStr">
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>仲間32体を集める</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>收集32全體精靈</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Collect 32 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 32마리 수집</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈蟲系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Bug-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bọ tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 벌레 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr"/>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>仲間32体を集める</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>收集32全體精靈</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Collect 32 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 32마리 수집</t>
-        </is>
-      </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の魅属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈蟲系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Bug-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Bọ tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 벌레 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12604,7 +12383,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -12624,7 +12403,7 @@
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -12677,7 +12456,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12687,7 +12465,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>仲間35体を集める</t>
+          <t>收集35名伙伴</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -12707,218 +12485,213 @@
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的岩石属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈岩石系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Stone DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đá tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 바위 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>仲間45体を集める</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>收集45全體精靈</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Collect 45 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 45마리 수집</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈岩石系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Stone DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Rock-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đá tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 바위 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>仲間45体を集める</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>收集45全體精靈</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Collect 45 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 45마리 수집</t>
-        </is>
-      </c>
-      <c r="F146" s="1" t="inlineStr">
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>仲間55体を集める</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>收集55全體精靈</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Collect 55 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 55마리 수집</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈岩石系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#Damage of all Rock-type attacks increases by #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I147" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đá tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J147" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 바위 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr"/>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>仲間55体を集める</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>收集55全體精靈</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Collect 55 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 55마리 수집</t>
-        </is>
-      </c>
-      <c r="F147" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の岩属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈岩石系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Rock-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Đá tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 바위 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12928,7 +12701,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -12948,7 +12721,7 @@
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -13001,7 +12774,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13011,7 +12783,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>仲間35体を集める</t>
+          <t>收集35名伙伴</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -13031,139 +12803,136 @@
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的黑暗属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈幽靈系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Dark DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Ma tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 고스트 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>仲間45体を集める</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>收集45全體精靈</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Collect 45 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 45마리 수집</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈幽靈系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Dark DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Ghost-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Ma tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 고스트 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr"/>
-      <c r="B150" s="1" t="inlineStr">
-        <is>
-          <t>仲間45体を集める</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>收集45全體精靈</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Collect 45 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 45마리 수집</t>
-        </is>
-      </c>
-      <c r="F150" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の暗属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈幽靈系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Ghost-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Ma tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 고스트 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13173,7 +12942,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -13193,7 +12962,7 @@
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -13246,7 +13015,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13256,7 +13024,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -13276,7 +13044,7 @@
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13329,7 +13097,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -13339,7 +13106,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>仲間36体を集める</t>
+          <t>收集36名伙伴</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -13359,139 +13126,136 @@
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的神属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈龍系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Divine DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Rồng tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 드래곤 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>仲間42体を集める</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>收集42全體精靈</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Collect 42 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 42마리 수집</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈龍系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Divine DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Dragon-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Rồng tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="J154" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 드래곤 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr"/>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>仲間42体を集める</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>收集42全體精靈</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Collect 42 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 42마리 수집</t>
-        </is>
-      </c>
-      <c r="F154" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の神属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈龍系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Dragon-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Rồng tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 드래곤 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13501,7 +13265,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>仲間20体を集める</t>
+          <t>收集20名伙伴</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -13521,7 +13285,7 @@
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -13574,7 +13338,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13584,7 +13347,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>仲間25体を集める</t>
+          <t>收集25名伙伴</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -13604,7 +13367,7 @@
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -13657,7 +13420,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13667,7 +13429,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -13687,139 +13449,136 @@
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的邪属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈惡系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Corrupt DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tối tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 악 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>仲間40体を集める</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>收集40全體精靈</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Collect 40 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 40마리 수집</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈惡系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Corrupt DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Dark-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tối tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="J158" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 악 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr"/>
-      <c r="B158" s="1" t="inlineStr">
-        <is>
-          <t>仲間40体を集める</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>收集40全體精靈</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Collect 40 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 40마리 수집</t>
-        </is>
-      </c>
-      <c r="F158" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の邪属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈惡系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Dark-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tối tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 악 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13829,7 +13588,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -13849,7 +13608,7 @@
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -13902,7 +13661,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13912,7 +13670,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -13932,7 +13690,7 @@
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -13985,7 +13743,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13995,7 +13752,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>仲間36体を集める</t>
+          <t>收集36名伙伴</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -14015,139 +13772,136 @@
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#所有伙伴的金属伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈鋼系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Metal DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thép tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 강철 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>仲間42体を集める</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>收集42全體精靈</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Collect 42 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 42마리 수집</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈鋼系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Metal DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Steel-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thép tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 강철 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" s="1" t="inlineStr">
-        <is>
-          <t>仲間42体を集める</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>收集42全體精靈</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Collect 42 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 42마리 수집</t>
-        </is>
-      </c>
-      <c r="F162" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の金属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈鋼系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Steel-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Thép tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 강철 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14157,7 +13911,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>仲間18体を集める</t>
+          <t>收集18名伙伴</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -14177,7 +13931,7 @@
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -14230,7 +13984,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -14240,7 +13993,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>仲間24体を集める</t>
+          <t>收集24名伙伴</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -14260,7 +14013,7 @@
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -14313,7 +14066,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14323,7 +14075,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>仲間30体を集める</t>
+          <t>收集30名伙伴</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -14343,139 +14095,136 @@
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
+          <t>#C0xFF5B545B#全体伙伴的精属性伤害+#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#全體精靈妖精系傷害加成提升#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#All Allies' Spirit DMG +#C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tiên tăng #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#전체 포켓몬 페어리 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>仲間40体を集める</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>收集40全體精靈</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Collect 40 of all Pokémons</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>전체 포켓몬 40마리 수집</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
           <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#全體精靈妖精系傷害加成提升#C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#All Allies' Spirit DMG +#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>#C0xFF5B545B#Damage of all Fairy-type attacks increases by #C0xFF60C456#1%</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
         <is>
           <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tiên tăng #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t>#C0xFF5B545B#전체 포켓몬 페어리 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t>仲間40体を集める</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>收集40全體精靈</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Collect 40 of all Pokémons</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>전체 포켓몬 40마리 수집</t>
-        </is>
-      </c>
-      <c r="F166" s="1" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#仲間全員の精属性ダメージ+#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#全體精靈妖精系傷害加成提升#C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#Damage of all Fairy-type attacks increases by #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B# Toàn bộ Pokémon - Tăng Thương Hệ Tiên tăng #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>#C0xFF5B545B#전체 포켓몬 페어리 타입 피해 보너스 증가: #C0xFF60C456#1%</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="Q166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
